--- a/output/pdf_financials_xlsx/NXT.xlsx
+++ b/output/pdf_financials_xlsx/NXT.xlsx
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.027203</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.191635</v>
+        <v>0.564933</v>
       </c>
     </row>
     <row r="93">
@@ -2738,7 +2738,11 @@
           <t>Reserve for warrants (Note 11)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.027203</v>
       </c>

--- a/output/pdf_financials_xlsx/NXT.xlsx
+++ b/output/pdf_financials_xlsx/NXT.xlsx
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.247677</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.42126</v>
       </c>
     </row>
     <row r="35">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.127628</v>
+        <v>0.375305</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.42126</v>
       </c>
     </row>
     <row r="37">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.274415</v>
+        <v>0.026738</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.442083</v>
+        <v>0.020823</v>
       </c>
     </row>
     <row r="49">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/NXT.xlsx
+++ b/output/pdf_financials_xlsx/NXT.xlsx
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.002153</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.123761</v>
       </c>
     </row>
     <row r="65">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.028014</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.053606</v>
       </c>
     </row>
     <row r="68">
